--- a/Myth_Busting_BOM.xlsx
+++ b/Myth_Busting_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDECF82C-D4F5-44F1-8179-C35FBDA62CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06D53349-F4D7-4ECA-BD3E-CF95D7D0C614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F00352C-CCE5-44C5-99CD-EA501ADF724C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Quantity</t>
   </si>
@@ -75,6 +75,18 @@
   </si>
   <si>
     <t>https://www.amazon.com/Deftun-Reader-Writer-Encoder-MSR605X/dp/B07FY6KH1X/ref=asc_df_B07FY6KH1X?tag=bingshoppinga-20&amp;linkCode=df0&amp;hvadid=80401998413302&amp;hvnetw=o&amp;hvqmt=e&amp;hvbmt=be&amp;hvdev=c&amp;hvlocint=&amp;hvlocphy=66994&amp;hvtargid=pla-4584001476806737&amp;psc=1&amp;msclkid=dd0f05c22e2b1aec72786c280995b2f4</t>
+  </si>
+  <si>
+    <t>Neodynium magnets</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/MAGABALLNET-Magnets-Neodymium-Refrigerator-Whiteboard/dp/B0F6ML1ZGB/ref=sr_1_3?dib=eyJ2IjoiMSJ9.nnecDr9DLJUGvGzX3z4JuwVGL0PpItN9p5yNpVRPBFfMu9A-xibsaCR75h7npD4hX8B0tu8q4-lvM9xASI9kQfxC8xJkpextx6BH6QyYiiAp8eC13jiP8Te5AQBxdDCLwirDQ8iwdr5qmz5LvNS08ufatb2SfmvWsSUATnQgMjz0AmgXfswio-NRv23eRS6H5SwNjBfyWsI1PUOFeQRsIGncwJ-xZ6yY1eXnSGPZZfI.mo4Io5VH1yjdRkQqJH-SnTDvcuGYeeTkTZugOvYY6tU&amp;dib_tag=se&amp;keywords=magnets%2Bof%2Bvarying%2Bstrength&amp;qid=1776954032&amp;sr=8-3&amp;th=1</t>
+  </si>
+  <si>
+    <t>200 Pack 5×2/6×2/8×2/6×3/8×3mm Strong Magnets</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -467,14 +479,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB61E678-4CFE-4916-B23D-EE587428F618}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="255.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -530,6 +541,32 @@
       </c>
       <c r="F3" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1">
+        <f>SUM(D2:D4)</f>
+        <v>128.32</v>
       </c>
     </row>
   </sheetData>
